--- a/OUTPUT/direct_Q88F34_Pseudomonas_putida_KT2440.xlsx
+++ b/OUTPUT/direct_Q88F34_Pseudomonas_putida_KT2440.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.659</v>
+        <v>0.6589364254298281</v>
       </c>
     </row>
   </sheetData>
